--- a/sample-data/ai-cashflow-variants/03-cua-hang-tien-loi-dem-24/input/02_sao_ke_hop_nhat.xlsx
+++ b/sample-data/ai-cashflow-variants/03-cua-hang-tien-loi-dem-24/input/02_sao_ke_hop_nhat.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R5a9fb046a4994093"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL_ACCOUNTS" sheetId="2" r:id="Ra8d4d84fbea04d93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R0d47c3562d834b15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL_ACCOUNTS" sheetId="2" r:id="Rcb5e2e36cec54c09"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/sample-data/ai-cashflow-variants/03-cua-hang-tien-loi-dem-24/input/02_sao_ke_hop_nhat.xlsx
+++ b/sample-data/ai-cashflow-variants/03-cua-hang-tien-loi-dem-24/input/02_sao_ke_hop_nhat.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R0d47c3562d834b15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL_ACCOUNTS" sheetId="2" r:id="Rcb5e2e36cec54c09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R5c2fe1880ef743a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL_ACCOUNTS" sheetId="2" r:id="R1b06d42a2fec4786"/>
   </x:sheets>
 </x:workbook>
 </file>
